--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-06</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-13</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13876.94</v>
+        <v>29892.7</v>
       </c>
       <c r="C3" t="n">
-        <v>13876.94</v>
+        <v>29892.7</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>975</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12027.33</v>
+        <v>20709.73</v>
       </c>
       <c r="C4" t="n">
-        <v>12027.33</v>
+        <v>20709.73</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>769</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16265.81</v>
+        <v>34689.62</v>
       </c>
       <c r="C5" t="n">
-        <v>16265.81</v>
+        <v>34689.62</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1116</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10872.97</v>
+        <v>21720.27</v>
       </c>
       <c r="C6" t="n">
-        <v>10872.97</v>
+        <v>21720.27</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>697</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3548.46</v>
+        <v>7392.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3548.46</v>
+        <v>7392.2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>299</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4726.07</v>
+        <v>9690.559999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>4726.07</v>
+        <v>9690.559999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>303</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61317.58</v>
+        <v>124095.08</v>
       </c>
       <c r="C9" t="n">
-        <v>61317.58</v>
+        <v>124095.08</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-13</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-20</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29892.7</v>
+        <v>47200.31</v>
       </c>
       <c r="C3" t="n">
-        <v>29892.7</v>
+        <v>47200.31</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2131</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20709.73</v>
+        <v>29402.46</v>
       </c>
       <c r="C4" t="n">
-        <v>20709.73</v>
+        <v>29402.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1371</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34689.62</v>
+        <v>54314.88</v>
       </c>
       <c r="C5" t="n">
-        <v>34689.62</v>
+        <v>54314.88</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2390</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21720.27</v>
+        <v>34535.71</v>
       </c>
       <c r="C6" t="n">
-        <v>21720.27</v>
+        <v>34535.71</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1415</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7392.2</v>
+        <v>14177.25</v>
       </c>
       <c r="C7" t="n">
-        <v>7392.2</v>
+        <v>14177.25</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>632</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9690.559999999999</v>
+        <v>17170.66</v>
       </c>
       <c r="C8" t="n">
-        <v>9690.559999999999</v>
+        <v>17170.66</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>626</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124095.08</v>
+        <v>196801.27</v>
       </c>
       <c r="C9" t="n">
-        <v>124095.08</v>
+        <v>196801.27</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-20</t>
+          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-27</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47200.31</v>
+        <v>65972.50999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>47200.31</v>
+        <v>65972.50999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3359</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29402.46</v>
+        <v>39111.17</v>
       </c>
       <c r="C4" t="n">
-        <v>29402.46</v>
+        <v>39111.17</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1951</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54314.88</v>
+        <v>73534.38</v>
       </c>
       <c r="C5" t="n">
-        <v>54314.88</v>
+        <v>73534.38</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3722</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34535.71</v>
+        <v>46005.36</v>
       </c>
       <c r="C6" t="n">
-        <v>34535.71</v>
+        <v>46005.36</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2200</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14177.25</v>
+        <v>18217.55</v>
       </c>
       <c r="C7" t="n">
-        <v>14177.25</v>
+        <v>18217.55</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1217</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17170.66</v>
+        <v>23548.23</v>
       </c>
       <c r="C8" t="n">
-        <v>17170.66</v>
+        <v>23548.23</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1023</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196801.27</v>
+        <v>266389.2</v>
       </c>
       <c r="C9" t="n">
-        <v>196801.27</v>
+        <v>266389.2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-01/2025-09-27</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-04</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65972.50999999999</v>
+        <v>9987.09</v>
       </c>
       <c r="C3" t="n">
-        <v>65972.50999999999</v>
+        <v>9987.09</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39111.17</v>
+        <v>6283.92</v>
       </c>
       <c r="C4" t="n">
-        <v>39111.17</v>
+        <v>6283.92</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2577</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73534.38</v>
+        <v>11053.17</v>
       </c>
       <c r="C5" t="n">
-        <v>73534.38</v>
+        <v>11053.17</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5023</v>
+        <v>756</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46005.36</v>
+        <v>8769.66</v>
       </c>
       <c r="C6" t="n">
-        <v>46005.36</v>
+        <v>8769.66</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2945</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18217.55</v>
+        <v>3432.69</v>
       </c>
       <c r="C7" t="n">
-        <v>18217.55</v>
+        <v>3432.69</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1589</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23548.23</v>
+        <v>3584.15</v>
       </c>
       <c r="C8" t="n">
-        <v>23548.23</v>
+        <v>3584.15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1414</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>266389.2</v>
+        <v>43110.68</v>
       </c>
       <c r="C9" t="n">
-        <v>266389.2</v>
+        <v>43110.68</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-04</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-11</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9987.09</v>
+        <v>27789.27</v>
       </c>
       <c r="C3" t="n">
-        <v>9987.09</v>
+        <v>27789.27</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>710</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6283.92</v>
+        <v>18019.85</v>
       </c>
       <c r="C4" t="n">
-        <v>6283.92</v>
+        <v>18019.85</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>393</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11053.17</v>
+        <v>31264.52</v>
       </c>
       <c r="C5" t="n">
-        <v>11053.17</v>
+        <v>31264.52</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>756</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8769.66</v>
+        <v>21478.25</v>
       </c>
       <c r="C6" t="n">
-        <v>8769.66</v>
+        <v>21478.25</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>573</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3432.69</v>
+        <v>9605.030000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>3432.69</v>
+        <v>9605.030000000001</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>292</v>
+        <v>808</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3584.15</v>
+        <v>9661.139999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>3584.15</v>
+        <v>9661.139999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>217</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43110.68</v>
+        <v>117818.06</v>
       </c>
       <c r="C9" t="n">
-        <v>43110.68</v>
+        <v>117818.06</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-11</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-18</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27789.27</v>
+        <v>47137.39</v>
       </c>
       <c r="C3" t="n">
-        <v>27789.27</v>
+        <v>47137.39</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1970</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18019.85</v>
+        <v>32178.38</v>
       </c>
       <c r="C4" t="n">
-        <v>18019.85</v>
+        <v>32178.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1153</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31264.52</v>
+        <v>49332.97</v>
       </c>
       <c r="C5" t="n">
-        <v>31264.52</v>
+        <v>49332.97</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2140</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21478.25</v>
+        <v>37719.8</v>
       </c>
       <c r="C6" t="n">
-        <v>21478.25</v>
+        <v>37719.8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1365</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9605.030000000001</v>
+        <v>13152.44</v>
       </c>
       <c r="C7" t="n">
-        <v>9605.030000000001</v>
+        <v>13152.44</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>808</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9661.139999999999</v>
+        <v>16310.77</v>
       </c>
       <c r="C8" t="n">
-        <v>9661.139999999999</v>
+        <v>16310.77</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>594</v>
+        <v>942</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117818.06</v>
+        <v>195831.75</v>
       </c>
       <c r="C9" t="n">
-        <v>117818.06</v>
+        <v>195831.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-18</t>
+          <t>multi-venue - Sales Summary - 2025-10-01/2025-10-25</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47137.39</v>
+        <v>62525.42</v>
       </c>
       <c r="C3" t="n">
-        <v>47137.39</v>
+        <v>62525.42</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3284</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32178.38</v>
+        <v>41669.38</v>
       </c>
       <c r="C4" t="n">
-        <v>32178.38</v>
+        <v>41669.38</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2056</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49332.97</v>
+        <v>65499.74</v>
       </c>
       <c r="C5" t="n">
-        <v>49332.97</v>
+        <v>65499.74</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3386</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37719.8</v>
+        <v>50700.46</v>
       </c>
       <c r="C6" t="n">
-        <v>37719.8</v>
+        <v>50700.46</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2297</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13152.44</v>
+        <v>19062.88</v>
       </c>
       <c r="C7" t="n">
-        <v>13152.44</v>
+        <v>19062.88</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1118</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16310.77</v>
+        <v>23143.51</v>
       </c>
       <c r="C8" t="n">
-        <v>16310.77</v>
+        <v>23143.51</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>942</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>195831.75</v>
+        <v>262601.39</v>
       </c>
       <c r="C9" t="n">
-        <v>195831.75</v>
+        <v>262601.39</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
